--- a/Dados/[Hapvida] Campanha junho_26.xlsx
+++ b/Dados/[Hapvida] Campanha junho_26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
   <bookViews>
-    <workbookView firstSheet="4" activeTab="3" tabRatio="500"/>
+    <workbookView tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" name="Individual copay total" sheetId="1"/>
@@ -311,7 +311,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9">
+  <fonts count="5">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -319,41 +319,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i val="0"/>
-      <color rgb="FFCC0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <color rgb="FFCC0000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -379,6 +344,13 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -403,26 +375,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-    </border>
-    <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
-      <bottom>
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -479,40 +437,83 @@
         <color rgb="FF000000"/>
       </top>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -772,7 +773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{81E20FED-91EE-4A4D-B763-8D6657340312}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{72F73568-38BE-4CF1-86B1-B72F2D5AF9DD}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T1001"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
   <cols>
@@ -806,13 +807,13 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -823,232 +824,232 @@
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>123.93</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>152.71</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>197.37</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>130.38</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>168.34</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>162.72</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>200.35</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>259.3</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>170.87</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>220.98</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>185.28</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>229.83</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>297.62</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>195.92</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>253.55</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>206.51</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>256.95</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>332.87</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>218.97</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>283.51</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>217.25</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>269.61</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>349.32</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>229.73</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>297.49</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>243.71</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>304.16</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>394.23</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>259.09</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>335.66</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>297.68</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>370.23</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>480.11</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>315.24</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>408.66</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>412.27</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>509.45</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>661.09</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>433.57</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>562.49</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>555.22</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>686.41</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>891.12</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>583.97</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>758</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>720.63</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>891.18</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>1157.3</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>758.01</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>984.26</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9" t="s">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="8"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -1059,202 +1060,202 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="10" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="10" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="10" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2246,7 +2247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C6B394EF-1391-4C9E-8778-A23471EC2024}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DF00EC1D-4506-4EAD-84A7-117C1217BD54}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T1001"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
   <cols>
@@ -2261,22 +2262,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13">
+      <c r="B1" s="11">
         <v>45100</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="11">
         <v>45097</v>
       </c>
-      <c r="D1" s="13">
+      <c r="D1" s="11">
         <v>45094</v>
       </c>
-      <c r="E1" s="13">
+      <c r="E1" s="11">
         <v>35768</v>
       </c>
-      <c r="F1" s="13">
+      <c r="F1" s="11">
         <v>35648</v>
       </c>
     </row>
@@ -2284,13 +2285,13 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -2299,239 +2300,239 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="14"/>
+      <c r="J2" s="12"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>147.9</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>182.52</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>236.11</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>155.72</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>201.29</v>
       </c>
-      <c r="J3" s="15"/>
+      <c r="J3" s="13"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>194.43</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>239.69</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>310.46</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>204.32</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>264.47</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>221.49</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>275.07</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>356.45</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>234.39</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>303.56</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="J5" s="13"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>246.95</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>307.62</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>398.76</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>262.05</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>339.53</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="13"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>259.83</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>322.81</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>418.51</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>274.96</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>356.31</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="13"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>291.57</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>364.27</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>472.42</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>310.2</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>402.11</v>
       </c>
-      <c r="J8" s="15"/>
+      <c r="J8" s="13"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>356.31</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>443.56</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>575.51</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>377.6</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>489.75</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="J9" s="13"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>493.77</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>610.65</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>792.74</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>519.63</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>674.39</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="13"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>665.24</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>823.03</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="4">
         <v>1068.85</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>700.15</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>909.08</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>863.66</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>1068.78</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>1388.35</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>909.04</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>1180.65</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9" t="s">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -2542,202 +2543,202 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>125.72</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="10">
         <v>155.14</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="10">
         <v>200.69</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="10">
         <v>132.36</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="10">
         <v>171.1</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="10">
         <v>165.27</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="10">
         <v>203.74</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="10">
         <v>263.89</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="10">
         <v>173.67</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="10">
         <v>224.8</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>188.27</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="10">
         <v>233.81</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="10">
         <v>302.98</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="10">
         <v>199.23</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="10">
         <v>258.03</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>209.91</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="10">
         <v>261.48</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="10">
         <v>338.95</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="10">
         <v>222.74</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <v>288.6</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="10">
         <v>220.86</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="10">
         <v>274.39</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="10">
         <v>355.73</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="10">
         <v>233.72</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <v>302.86</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="10">
         <v>247.83</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="10">
         <v>309.63</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="10">
         <v>401.56</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="10">
         <v>263.67</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <v>341.79</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="10">
         <v>302.86</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="10">
         <v>377.03</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="10">
         <v>489.18</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="10">
         <v>320.96</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <v>416.29</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="10">
         <v>419.7</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="10">
         <v>519.05</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="10">
         <v>673.83</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="10">
         <v>441.69</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="10">
         <v>573.23</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="10">
         <v>565.45</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="10">
         <v>699.58</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="10">
         <v>908.52</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="10">
         <v>595.13</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <v>772.72</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="10">
         <v>734.11</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="10">
         <v>908.46</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="14">
         <v>1180.1</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="10">
         <v>772.68</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="14">
         <v>1003.55</v>
       </c>
     </row>
@@ -3730,7 +3731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{E9E6F058-576A-4FC1-977B-B069AC6C0532}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C6275650-0B96-46AE-94B4-35535BD96181}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:T1000"/>
   <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
   <cols>
@@ -3747,50 +3748,50 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4787,7 +4788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{95B0E812-42C9-4FA0-B6EF-603342C9283C}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BF456922-86CC-49DD-A3D2-8219B6016863}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -4829,574 +4830,574 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="18"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3">
         <v>162.67</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <v>243.23</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>120.88</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="3">
         <v>180.58</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3">
         <v>102.99</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="3">
         <v>153.72</v>
       </c>
-      <c r="J3" s="15"/>
-      <c r="K3" s="18"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3">
         <v>182.19</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>272.42</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>135.39</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="3">
         <v>202.25</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>115.35</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="3">
         <v>172.17</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="18"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3">
         <v>204.05</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>305.11</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>151.64</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>226.52</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="3">
         <v>129.19</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="3">
         <v>192.83</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="18"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3">
         <v>234.66</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <v>350.88</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>174.39</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="3">
         <v>260.5</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="3">
         <v>148.57</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="3">
         <v>221.75</v>
       </c>
-      <c r="J6" s="15"/>
-      <c r="K6" s="18"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
         <v>269.86</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <v>403.51</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>200.55</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="3">
         <v>299.58</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <v>170.86</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="3">
         <v>255.01</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="18"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3">
         <v>321.13</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>480.18</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>238.65</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="3">
         <v>356.5</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="3">
         <v>203.32</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="3">
         <v>303.46</v>
       </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="18"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3">
         <v>401.41</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>600.23</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>298.31</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="3">
         <v>445.63</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="3">
         <v>254.15</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="3">
         <v>379.33</v>
       </c>
-      <c r="J9" s="15"/>
-      <c r="K9" s="18"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3">
         <v>501.76</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>750.29</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>372.89</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="3">
         <v>557.04</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="3">
         <v>317.69</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="3">
         <v>474.16</v>
       </c>
-      <c r="J10" s="15"/>
-      <c r="K10" s="18"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3">
         <v>852.99</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>1275.49</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>633.91</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="3">
         <v>946.97</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="3">
         <v>540.07</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="3">
         <v>806.07</v>
       </c>
-      <c r="J11" s="15"/>
-      <c r="K11" s="18"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3">
         <v>955.35</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>1428.55</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>709.98</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="3">
         <v>1060.61</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="3">
         <v>604.88</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="3">
         <v>902.8</v>
       </c>
-      <c r="J12" s="15"/>
-      <c r="K12" s="18"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="10"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="8"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="12">
+      <c r="B15" s="3"/>
+      <c r="C15" s="10">
         <v>138.27</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="10">
         <v>206.75</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="10">
         <v>102.75</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="10">
         <v>153.49</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="10">
         <v>87.54</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="10">
         <v>130.66</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="12">
+      <c r="B16" s="3"/>
+      <c r="C16" s="10">
         <v>154.86</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="10">
         <v>231.56</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="10">
         <v>115.08</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="10">
         <v>171.91</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="10">
         <v>98.05</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="10">
         <v>146.34</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="12">
+      <c r="B17" s="3"/>
+      <c r="C17" s="10">
         <v>173.44</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="10">
         <v>259.34</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="10">
         <v>128.89</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="10">
         <v>192.54</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="10">
         <v>109.81</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="10">
         <v>163.91</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="12">
+      <c r="B18" s="3"/>
+      <c r="C18" s="10">
         <v>199.46</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="10">
         <v>298.25</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="10">
         <v>148.23</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="10">
         <v>221.43</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="10">
         <v>126.28</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="10">
         <v>188.49</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="12">
+      <c r="B19" s="3"/>
+      <c r="C19" s="10">
         <v>229.38</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="10">
         <v>342.98</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="10">
         <v>170.47</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="10">
         <v>254.64</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="10">
         <v>145.23</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="10">
         <v>216.76</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="12">
+      <c r="B20" s="3"/>
+      <c r="C20" s="10">
         <v>272.96</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="10">
         <v>408.15</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="10">
         <v>202.85</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="10">
         <v>303.03</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="10">
         <v>172.82</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="10">
         <v>257.94</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="12">
+      <c r="B21" s="3"/>
+      <c r="C21" s="10">
         <v>341.2</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="10">
         <v>510.2</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="10">
         <v>253.56</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <v>378.79</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="10">
         <v>216.03</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="10">
         <v>322.43</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="12">
+      <c r="B22" s="3"/>
+      <c r="C22" s="10">
         <v>426.5</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="10">
         <v>637.75</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="10">
         <v>316.96</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="10">
         <v>473.48</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="10">
         <v>270.04</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="10">
         <v>403.04</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="12">
+      <c r="B23" s="3"/>
+      <c r="C23" s="10">
         <v>725.04</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="10">
         <v>1084.17</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="10">
         <v>538.82</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="10">
         <v>804.92</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="10">
         <v>459.06</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="10">
         <v>685.16</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="12">
+      <c r="B24" s="3"/>
+      <c r="C24" s="10">
         <v>812.05</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="10">
         <v>1214.27</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="10">
         <v>603.48</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="10">
         <v>901.52</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="10">
         <v>514.15</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="10">
         <v>767.38</v>
       </c>
     </row>
   </sheetData>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
@@ -5406,7 +5407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{7FB20B19-AC53-453F-9AB2-8BC3CA85877C}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{017DE0E0-0137-4F80-B348-7102E989050B}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -5449,503 +5450,503 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="18">
         <v>131.3</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="18">
         <v>196.18</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="18">
         <v>95.76</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="18">
         <v>142.88</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="18">
         <v>81.62</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="18">
         <v>121.68</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="18">
         <v>147.06</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="18">
         <v>219.72</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="18">
         <v>107.25</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="18">
         <v>160.03</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="18">
         <v>91.41</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="18">
         <v>136.28</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="18">
         <v>164.71</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="18">
         <v>246.09</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="18">
         <v>120.12</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="18">
         <v>179.23</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="18">
         <v>102.38</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="18">
         <v>152.63</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="18">
         <v>189.42</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="18">
         <v>283</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="18">
         <v>138.14</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="18">
         <v>206.11</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="18">
         <v>117.74</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="18">
         <v>175.52</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="18">
         <v>217.83</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="18">
         <v>325.45</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="18">
         <v>158.86</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="18">
         <v>237.03</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="18">
         <v>135.4</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="18">
         <v>201.85</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="18">
         <v>259.22</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="18">
         <v>387.29</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="18">
         <v>189.04</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="18">
         <v>282.07</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="18">
         <v>161.13</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="18">
         <v>240.2</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="18">
         <v>324.03</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="18">
         <v>484.11</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="18">
         <v>236.3</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="18">
         <v>352.59</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="18">
         <v>201.41</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="18">
         <v>300.25</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="18">
         <v>405.04</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="18">
         <v>605.14</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="18">
         <v>295.38</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="18">
         <v>440.74</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="18">
         <v>251.76</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="18">
         <v>375.31</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="18">
         <v>688.57</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="18">
         <v>1028.74</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="18">
         <v>502.15</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="18">
         <v>749.26</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="18">
         <v>427.99</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="18">
         <v>638.03</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="18">
         <v>771.2</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="18">
         <v>1152.19</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="18">
         <v>562.41</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="18">
         <v>839.17</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="18">
         <v>479.35</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="18">
         <v>714.59</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="5"/>
+      <c r="B13" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="17" t="s">
+      <c r="G14" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="21">
+      <c r="A15" s="3"/>
+      <c r="B15" s="18">
         <v>111.61</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="18">
         <v>166.75</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="18">
         <v>81.4</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="18">
         <v>121.45</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="18">
         <v>69.38</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="18">
         <v>103.43</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="21">
+      <c r="A16" s="3"/>
+      <c r="B16" s="18">
         <v>125</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="18">
         <v>186.76</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="18">
         <v>91.16</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="18">
         <v>136.03</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="18">
         <v>77.7</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="18">
         <v>115.84</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="21">
+      <c r="A17" s="3"/>
+      <c r="B17" s="18">
         <v>140</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="18">
         <v>209.18</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="18">
         <v>102.1</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="18">
         <v>152.35</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="18">
         <v>87.02</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="18">
         <v>129.74</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="21">
+      <c r="A18" s="3"/>
+      <c r="B18" s="18">
         <v>161.01</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="18">
         <v>240.55</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="18">
         <v>117.42</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="18">
         <v>175.19</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="18">
         <v>100.08</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="18">
         <v>149.19</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="21">
+      <c r="A19" s="3"/>
+      <c r="B19" s="18">
         <v>185.16</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="18">
         <v>276.63</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="18">
         <v>135.03</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="18">
         <v>201.48</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="18">
         <v>115.09</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="18">
         <v>171.57</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="21">
+      <c r="A20" s="3"/>
+      <c r="B20" s="18">
         <v>220.34</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="18">
         <v>329.2</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="18">
         <v>160.68</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="18">
         <v>239.76</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="18">
         <v>136.96</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="18">
         <v>204.17</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="21">
+      <c r="A21" s="3"/>
+      <c r="B21" s="18">
         <v>275.43</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="18">
         <v>411.49</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="18">
         <v>200.86</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="18">
         <v>299.7</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="18">
         <v>171.2</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="18">
         <v>255.21</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="21">
+      <c r="A22" s="3"/>
+      <c r="B22" s="18">
         <v>344.28</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="18">
         <v>514.37</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="18">
         <v>251.07</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="18">
         <v>374.63</v>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="18">
         <v>214</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="18">
         <v>319.01</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="21">
+      <c r="A23" s="3"/>
+      <c r="B23" s="18">
         <v>585.28</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="18">
         <v>874.43</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="18">
         <v>426.83</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="18">
         <v>636.87</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="18">
         <v>363.79</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="18">
         <v>542.33</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="21">
+      <c r="A24" s="3"/>
+      <c r="B24" s="18">
         <v>655.52</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="18">
         <v>979.36</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="18">
         <v>478.05</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="18">
         <v>713.29</v>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="18">
         <v>407.45</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="18">
         <v>607.4</v>
       </c>
     </row>
   </sheetData>
   <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
     <oddFooter>&amp;L&amp;C&amp;R</oddFooter>

--- a/Dados/[Hapvida] Campanha junho_26.xlsx
+++ b/Dados/[Hapvida] Campanha junho_26.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView tabRatio="500"/>
-  </bookViews>
   <sheets>
-    <sheet r:id="rId1" name="Individual copay total" sheetId="1"/>
-    <sheet r:id="rId2" name="Individual copay parcial" sheetId="2"/>
-    <sheet r:id="rId3" name="Coparticipação" sheetId="3"/>
-    <sheet r:id="rId4" name="Super Simples Parcial" sheetId="4"/>
-    <sheet r:id="rId5" name="Super Simples Total" sheetId="5"/>
+    <sheet state="visible" name="Individual copay total" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Individual copay parcial" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Coparticipação" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Super Simples Parcial" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Super Simples Total" sheetId="5" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
+  <definedNames/>
+  <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="z/vVW3MRdcGiR6WzbGcrFkFZyA1XGinYwfHYHhIext8="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="96">
   <si>
     <t>Código</t>
   </si>
@@ -310,44 +313,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="6">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <i val="0"/>
-      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <i val="0"/>
-      <sz val="11"/>
       <color rgb="FFCC0000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="11"/>
       <color rgb="FFCC0000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
@@ -357,31 +354,29 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
+  <borders count="6">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -437,125 +432,101 @@
         <color rgb="FF000000"/>
       </top>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+  <cellXfs count="23">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="1"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <bag type="Checkbox"/>
-  <bag type="XFControls">
-    <bagId k="CellControl">0</bagId>
-  </bag>
-  <bag type="XFComplement">
-    <bagId k="XFControls">1</bagId>
-  </bag>
-  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
-    <a k="MappedFeaturePropertyBags">
-      <bagId>2</bagId>
-    </a>
-  </bag>
-</FeaturePropertyBags>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -592,12 +563,12 @@
       <a:majorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface="Calibri"/>
-        <a:cs typeface=""/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface="Calibri"/>
-        <a:cs typeface=""/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -609,211 +580,182 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{72F73568-38BE-4CF1-86B1-B72F2D5AF9DD}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:T1001"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.00390625" customWidth="1"/>
-    <col min="2" max="2" width="25.28125" customWidth="1"/>
-    <col min="3" max="6" width="22.00390625" customWidth="1"/>
-    <col min="7" max="27" width="8.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="22.0"/>
+    <col customWidth="1" min="2" max="2" width="25.29"/>
+    <col customWidth="1" min="3" max="6" width="22.0"/>
+    <col customWidth="1" min="7" max="27" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>45099</v>
+        <v>45099.0</v>
       </c>
       <c r="C1" s="1">
-        <v>45096</v>
+        <v>45096.0</v>
       </c>
       <c r="D1" s="1">
-        <v>45093</v>
+        <v>45093.0</v>
       </c>
       <c r="E1" s="1">
-        <v>35767</v>
+        <v>35767.0</v>
       </c>
       <c r="F1" s="1">
-        <v>35649</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+        <v>35649.0</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -823,233 +765,233 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="3" t="s">
+    <row r="3">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>123.93</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>152.71</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>197.37</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>130.38</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>168.34</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>162.72</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>200.35</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>259.3</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>170.87</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>220.98</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="3" t="s">
+    <row r="5">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>185.28</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>229.83</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>297.62</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>195.92</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>253.55</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="3" t="s">
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>206.51</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>256.95</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <v>332.87</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>218.97</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>283.51</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="3" t="s">
+    <row r="7">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>217.25</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>269.61</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <v>349.32</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>229.73</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>297.49</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="3" t="s">
+    <row r="8">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>243.71</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>304.16</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <v>394.23</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>259.09</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>335.66</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="3" t="s">
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>297.68</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>370.23</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>480.11</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>315.24</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>408.66</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="3" t="s">
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>412.27</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>509.45</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>661.09</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>433.57</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>562.49</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="3" t="s">
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>555.22</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>686.41</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="5">
         <v>891.12</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>583.97</v>
       </c>
-      <c r="F11" s="3">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="F11" s="4">
+        <v>758.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>720.63</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>891.18</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="6">
         <v>1157.3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>758.01</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>984.26</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7" t="s">
+    <row r="15">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="8"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="10"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+    </row>
+    <row r="16">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
@@ -1059,203 +1001,203 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3" t="s">
+    <row r="17">
+      <c r="A17" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="3" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="3" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="3" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="3" t="s">
+    <row r="21">
+      <c r="A21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="12" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="12" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2236,62 +2178,60 @@
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="landscape"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{DF00EC1D-4506-4EAD-84A7-117C1217BD54}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:T1001"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.00390625" customWidth="1"/>
-    <col min="2" max="2" width="25.28125" customWidth="1"/>
-    <col min="3" max="3" width="22.00390625" customWidth="1"/>
-    <col min="4" max="4" width="20.57421875" customWidth="1"/>
-    <col min="5" max="6" width="22.00390625" customWidth="1"/>
-    <col min="7" max="9" width="8.7109375" customWidth="1"/>
-    <col min="10" max="10" width="13.57421875" customWidth="1"/>
-    <col min="11" max="27" width="8.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="22.0"/>
+    <col customWidth="1" min="2" max="2" width="25.29"/>
+    <col customWidth="1" min="3" max="3" width="22.0"/>
+    <col customWidth="1" min="4" max="4" width="20.57"/>
+    <col customWidth="1" min="5" max="6" width="22.0"/>
+    <col customWidth="1" min="7" max="9" width="8.71"/>
+    <col customWidth="1" min="10" max="10" width="13.57"/>
+    <col customWidth="1" min="11" max="27" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11">
-        <v>45100</v>
-      </c>
-      <c r="C1" s="11">
-        <v>45097</v>
-      </c>
-      <c r="D1" s="11">
-        <v>45094</v>
-      </c>
-      <c r="E1" s="11">
-        <v>35768</v>
-      </c>
-      <c r="F1" s="11">
-        <v>35648</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+      <c r="B1" s="13">
+        <v>45100.0</v>
+      </c>
+      <c r="C1" s="13">
+        <v>45097.0</v>
+      </c>
+      <c r="D1" s="13">
+        <v>45094.0</v>
+      </c>
+      <c r="E1" s="13">
+        <v>35768.0</v>
+      </c>
+      <c r="F1" s="13">
+        <v>35648.0</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -2300,239 +2240,239 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="12"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>147.9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>182.52</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>236.11</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="4">
         <v>155.72</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>201.29</v>
       </c>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>194.43</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>239.69</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>310.46</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="4">
         <v>204.32</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="4">
         <v>264.47</v>
       </c>
-      <c r="J4" s="13"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="J4" s="15"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>221.49</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>275.07</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>356.45</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>234.39</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>303.56</v>
       </c>
-      <c r="J5" s="13"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>246.95</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>307.62</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <v>398.76</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>262.05</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>339.53</v>
       </c>
-      <c r="J6" s="13"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="J6" s="15"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>259.83</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>322.81</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <v>418.51</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>274.96</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>356.31</v>
       </c>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>291.57</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>364.27</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <v>472.42</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>310.2</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>402.11</v>
       </c>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>356.31</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>443.56</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>575.51</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>377.6</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>489.75</v>
       </c>
-      <c r="J9" s="13"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="J9" s="15"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>493.77</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>610.65</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>792.74</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>519.63</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>674.39</v>
       </c>
-      <c r="J10" s="13"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>665.24</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>823.03</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="6">
         <v>1068.85</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>700.15</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>909.08</v>
       </c>
-      <c r="J11" s="13"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="J11" s="15"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>863.66</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>1068.78</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="6">
         <v>1388.35</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>909.04</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>1180.65</v>
       </c>
-      <c r="J12" s="13"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7" t="s">
+      <c r="J12" s="15"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15">
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -2542,203 +2482,203 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="3" t="s">
+    <row r="16">
+      <c r="A16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="12">
         <v>125.72</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="12">
         <v>155.14</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="12">
         <v>200.69</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="12">
         <v>132.36</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="12">
         <v>171.1</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3" t="s">
+    <row r="17">
+      <c r="A17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="12">
         <v>165.27</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="12">
         <v>203.74</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="12">
         <v>263.89</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="12">
         <v>173.67</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="12">
         <v>224.8</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="3" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="12">
         <v>188.27</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="12">
         <v>233.81</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="12">
         <v>302.98</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="12">
         <v>199.23</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="12">
         <v>258.03</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="3" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="12">
         <v>209.91</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="12">
         <v>261.48</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="12">
         <v>338.95</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="12">
         <v>222.74</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="12">
         <v>288.6</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="3" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="12">
         <v>220.86</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="12">
         <v>274.39</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="12">
         <v>355.73</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="12">
         <v>233.72</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="12">
         <v>302.86</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="3" t="s">
+    <row r="21">
+      <c r="A21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="12">
         <v>247.83</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="12">
         <v>309.63</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="12">
         <v>401.56</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="12">
         <v>263.67</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="12">
         <v>341.79</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="12">
         <v>302.86</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="12">
         <v>377.03</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="12">
         <v>489.18</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="12">
         <v>320.96</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <v>416.29</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="12">
         <v>419.7</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="12">
         <v>519.05</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="12">
         <v>673.83</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="12">
         <v>441.69</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="12">
         <v>573.23</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="12">
         <v>565.45</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="12">
         <v>699.58</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="12">
         <v>908.52</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="12">
         <v>595.13</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="12">
         <v>772.72</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="12">
         <v>734.11</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="12">
         <v>908.46</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="16">
         <v>1180.1</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="12">
         <v>772.68</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="16">
         <v>1003.55</v>
       </c>
     </row>
@@ -3720,26 +3660,24 @@
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="landscape"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{C6275650-0B96-46AE-94B4-35535BD96181}" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:T1000"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="2" width="22.00390625" customWidth="1"/>
-    <col min="3" max="26" width="8.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="2" width="22.0"/>
+    <col customWidth="1" min="3" max="26" width="8.71"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -3747,51 +3685,51 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2">
+      <c r="A2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="3" t="s">
+    <row r="3">
+      <c r="A3" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row r="4">
+      <c r="A4" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="3" t="s">
+    <row r="5">
+      <c r="A5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="3" t="s">
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="3" t="s">
+    <row r="7">
+      <c r="A7" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4777,1180 +4715,1160 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="landscape"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{BF456922-86CC-49DD-A3D2-8219B6016863}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T200"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="2" max="2" width="25.00390625" customWidth="1"/>
-    <col min="3" max="3" width="19.28125" customWidth="1"/>
-    <col min="4" max="4" width="18.57421875" customWidth="1"/>
-    <col min="5" max="7" width="18.00390625" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
+    <col customWidth="1" min="2" max="2" width="25.0"/>
+    <col customWidth="1" min="3" max="3" width="19.29"/>
+    <col customWidth="1" min="4" max="4" width="18.57"/>
+    <col customWidth="1" min="5" max="7" width="18.0"/>
+    <col customWidth="1" min="8" max="8" width="19.14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1">
-        <v>21218</v>
+        <v>21218.0</v>
       </c>
       <c r="D1" s="1">
-        <v>21219</v>
+        <v>21219.0</v>
       </c>
       <c r="E1" s="1">
-        <v>45059</v>
+        <v>45059.0</v>
       </c>
       <c r="F1" s="1">
-        <v>45069</v>
+        <v>45069.0</v>
       </c>
       <c r="G1" s="1">
-        <v>35577</v>
+        <v>35577.0</v>
       </c>
       <c r="H1" s="1">
-        <v>35585</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+        <v>35585.0</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="J2" s="14"/>
+      <c r="K2" s="19"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3">
+      <c r="B3" s="4"/>
+      <c r="C3" s="5">
         <v>162.67</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="5">
         <v>243.23</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="5">
         <v>120.88</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="5">
         <v>180.58</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="5">
         <v>102.99</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="5">
         <v>153.72</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="J3" s="15"/>
+      <c r="K3" s="19"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5">
         <v>182.19</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>272.42</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="5">
         <v>135.39</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="5">
         <v>202.25</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <v>115.35</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>172.17</v>
       </c>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="3" t="s">
+      <c r="J4" s="15"/>
+      <c r="K4" s="19"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5">
         <v>204.05</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>305.11</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="5">
         <v>151.64</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="5">
         <v>226.52</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <v>129.19</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="5">
         <v>192.83</v>
       </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="J5" s="15"/>
+      <c r="K5" s="19"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3">
+      <c r="B6" s="4"/>
+      <c r="C6" s="5">
         <v>234.66</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="5">
         <v>350.88</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="5">
         <v>174.39</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="5">
         <v>260.5</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <v>148.57</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="5">
         <v>221.75</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="3" t="s">
+      <c r="J6" s="15"/>
+      <c r="K6" s="19"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5">
         <v>269.86</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="5">
         <v>403.51</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="5">
         <v>200.55</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="5">
         <v>299.58</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="5">
         <v>170.86</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="5">
         <v>255.01</v>
       </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="3" t="s">
+      <c r="J7" s="15"/>
+      <c r="K7" s="19"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5">
         <v>321.13</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <v>480.18</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="5">
         <v>238.65</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="5">
         <v>356.5</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="5">
         <v>203.32</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="5">
         <v>303.46</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="3" t="s">
+      <c r="J8" s="15"/>
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5">
         <v>401.41</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>600.23</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="5">
         <v>298.31</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="5">
         <v>445.63</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="5">
         <v>254.15</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="5">
         <v>379.33</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="3" t="s">
+      <c r="J9" s="15"/>
+      <c r="K9" s="19"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5">
         <v>501.76</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>750.29</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="5">
         <v>372.89</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="5">
         <v>557.04</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="5">
         <v>317.69</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="5">
         <v>474.16</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="3" t="s">
+      <c r="J10" s="15"/>
+      <c r="K10" s="19"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5">
         <v>852.99</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="5">
         <v>1275.49</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="5">
         <v>633.91</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="5">
         <v>946.97</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="5">
         <v>540.07</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="5">
         <v>806.07</v>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="16" t="s">
+      <c r="J11" s="15"/>
+      <c r="K11" s="19"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5">
         <v>955.35</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="5">
         <v>1428.55</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="5">
         <v>709.98</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="5">
         <v>1060.61</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <v>604.88</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="5">
         <v>902.8</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7" t="s">
+      <c r="J12" s="15"/>
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="8"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="10"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="3" t="s">
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="10">
+      <c r="B15" s="4"/>
+      <c r="C15" s="12">
         <v>138.27</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="12">
         <v>206.75</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="12">
         <v>102.75</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="12">
         <v>153.49</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="12">
         <v>87.54</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="12">
         <v>130.66</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="3" t="s">
+    <row r="16">
+      <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="10">
+      <c r="B16" s="4"/>
+      <c r="C16" s="12">
         <v>154.86</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="12">
         <v>231.56</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="12">
         <v>115.08</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="12">
         <v>171.91</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="12">
         <v>98.05</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="12">
         <v>146.34</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3" t="s">
+    <row r="17">
+      <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="10">
+      <c r="B17" s="4"/>
+      <c r="C17" s="12">
         <v>173.44</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="12">
         <v>259.34</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="12">
         <v>128.89</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="12">
         <v>192.54</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="12">
         <v>109.81</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="12">
         <v>163.91</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="3" t="s">
+    <row r="18">
+      <c r="A18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="10">
+      <c r="B18" s="4"/>
+      <c r="C18" s="12">
         <v>199.46</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="12">
         <v>298.25</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="12">
         <v>148.23</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="12">
         <v>221.43</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="12">
         <v>126.28</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="12">
         <v>188.49</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="3" t="s">
+    <row r="19">
+      <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="10">
+      <c r="B19" s="4"/>
+      <c r="C19" s="12">
         <v>229.38</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="12">
         <v>342.98</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="12">
         <v>170.47</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="12">
         <v>254.64</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="12">
         <v>145.23</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="12">
         <v>216.76</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="3" t="s">
+    <row r="20">
+      <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="10">
+      <c r="B20" s="4"/>
+      <c r="C20" s="12">
         <v>272.96</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="12">
         <v>408.15</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="12">
         <v>202.85</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="12">
         <v>303.03</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="12">
         <v>172.82</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="12">
         <v>257.94</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="3" t="s">
+    <row r="21">
+      <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="10">
+      <c r="B21" s="4"/>
+      <c r="C21" s="12">
         <v>341.2</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="12">
         <v>510.2</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="12">
         <v>253.56</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="12">
         <v>378.79</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="12">
         <v>216.03</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="12">
         <v>322.43</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="3" t="s">
+    <row r="22">
+      <c r="A22" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="10">
+      <c r="B22" s="4"/>
+      <c r="C22" s="12">
         <v>426.5</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="12">
         <v>637.75</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="12">
         <v>316.96</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="12">
         <v>473.48</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="12">
         <v>270.04</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="12">
         <v>403.04</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="3" t="s">
+    <row r="23">
+      <c r="A23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="10">
+      <c r="B23" s="4"/>
+      <c r="C23" s="12">
         <v>725.04</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="12">
         <v>1084.17</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="12">
         <v>538.82</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="12">
         <v>804.92</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="12">
         <v>459.06</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="12">
         <v>685.16</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="3" t="s">
+    <row r="24">
+      <c r="A24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="10">
+      <c r="B24" s="4"/>
+      <c r="C24" s="12">
         <v>812.05</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="12">
         <v>1214.27</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="12">
         <v>603.48</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="12">
         <v>901.52</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="12">
         <v>514.15</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="12">
         <v>767.38</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{017DE0E0-0137-4F80-B348-7102E989050B}" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T200"/>
-  <sheetFormatPr defaultRowHeight="15" defaultColWidth="14.421875" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.57421875" customWidth="1"/>
-    <col min="2" max="2" width="22.00390625" customWidth="1"/>
-    <col min="3" max="3" width="22.28125" customWidth="1"/>
-    <col min="4" max="4" width="17.421875" customWidth="1"/>
-    <col min="5" max="5" width="16.8515625" customWidth="1"/>
-    <col min="6" max="6" width="18.421875" customWidth="1"/>
-    <col min="7" max="7" width="18.57421875" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="19.57"/>
+    <col customWidth="1" min="2" max="2" width="22.0"/>
+    <col customWidth="1" min="3" max="3" width="22.29"/>
+    <col customWidth="1" min="4" max="4" width="17.43"/>
+    <col customWidth="1" min="5" max="5" width="16.86"/>
+    <col customWidth="1" min="6" max="6" width="18.43"/>
+    <col customWidth="1" min="7" max="7" width="18.57"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>11791</v>
+        <v>11791.0</v>
       </c>
       <c r="C1" s="1">
-        <v>11790</v>
+        <v>11790.0</v>
       </c>
       <c r="D1" s="1">
-        <v>45058</v>
+        <v>45058.0</v>
       </c>
       <c r="E1" s="1">
-        <v>45068</v>
+        <v>45068.0</v>
       </c>
       <c r="F1" s="1">
-        <v>35493</v>
+        <v>35493.0</v>
       </c>
       <c r="G1" s="1">
-        <v>35509</v>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+        <v>35509.0</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="17" t="s">
+    <row r="3">
+      <c r="A3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="22">
         <v>131.3</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="22">
         <v>196.18</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="22">
         <v>95.76</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="22">
         <v>142.88</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="22">
         <v>81.62</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="22">
         <v>121.68</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="17" t="s">
+    <row r="4">
+      <c r="A4" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="22">
         <v>147.06</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="22">
         <v>219.72</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="22">
         <v>107.25</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="22">
         <v>160.03</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="22">
         <v>91.41</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="22">
         <v>136.28</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="17" t="s">
+    <row r="5">
+      <c r="A5" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="22">
         <v>164.71</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="22">
         <v>246.09</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="22">
         <v>120.12</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="22">
         <v>179.23</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="22">
         <v>102.38</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="22">
         <v>152.63</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="17" t="s">
+    <row r="6">
+      <c r="A6" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="22">
         <v>189.42</v>
       </c>
-      <c r="C6" s="18">
-        <v>283</v>
-      </c>
-      <c r="D6" s="18">
+      <c r="C6" s="22">
+        <v>283.0</v>
+      </c>
+      <c r="D6" s="22">
         <v>138.14</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="22">
         <v>206.11</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="22">
         <v>117.74</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="22">
         <v>175.52</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="17" t="s">
+    <row r="7">
+      <c r="A7" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="22">
         <v>217.83</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="22">
         <v>325.45</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="22">
         <v>158.86</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="22">
         <v>237.03</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="22">
         <v>135.4</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="22">
         <v>201.85</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="17" t="s">
+    <row r="8">
+      <c r="A8" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="22">
         <v>259.22</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="22">
         <v>387.29</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="22">
         <v>189.04</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="22">
         <v>282.07</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="22">
         <v>161.13</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="22">
         <v>240.2</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="17" t="s">
+    <row r="9">
+      <c r="A9" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="22">
         <v>324.03</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="22">
         <v>484.11</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="22">
         <v>236.3</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="22">
         <v>352.59</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="22">
         <v>201.41</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="22">
         <v>300.25</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="17" t="s">
+    <row r="10">
+      <c r="A10" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="22">
         <v>405.04</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="22">
         <v>605.14</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="22">
         <v>295.38</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="22">
         <v>440.74</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="22">
         <v>251.76</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="22">
         <v>375.31</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="17" t="s">
+    <row r="11">
+      <c r="A11" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="22">
         <v>688.57</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="22">
         <v>1028.74</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="22">
         <v>502.15</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="22">
         <v>749.26</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="22">
         <v>427.99</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="22">
         <v>638.03</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="17" t="s">
+    <row r="12">
+      <c r="A12" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="22">
         <v>771.2</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="22">
         <v>1152.19</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="22">
         <v>562.41</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="22">
         <v>839.17</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="22">
         <v>479.35</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="22">
         <v>714.59</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="5"/>
-      <c r="B13" s="7" t="s">
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14">
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="3"/>
-      <c r="B15" s="18">
+    <row r="15">
+      <c r="A15" s="4"/>
+      <c r="B15" s="22">
         <v>111.61</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="22">
         <v>166.75</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="22">
         <v>81.4</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="22">
         <v>121.45</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="22">
         <v>69.38</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="22">
         <v>103.43</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="3"/>
-      <c r="B16" s="18">
-        <v>125</v>
-      </c>
-      <c r="C16" s="18">
+    <row r="16">
+      <c r="A16" s="4"/>
+      <c r="B16" s="22">
+        <v>125.0</v>
+      </c>
+      <c r="C16" s="22">
         <v>186.76</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="22">
         <v>91.16</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="22">
         <v>136.03</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="22">
         <v>77.7</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="22">
         <v>115.84</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3"/>
-      <c r="B17" s="18">
-        <v>140</v>
-      </c>
-      <c r="C17" s="18">
+    <row r="17">
+      <c r="A17" s="4"/>
+      <c r="B17" s="22">
+        <v>140.0</v>
+      </c>
+      <c r="C17" s="22">
         <v>209.18</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="22">
         <v>102.1</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="22">
         <v>152.35</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="22">
         <v>87.02</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="22">
         <v>129.74</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="3"/>
-      <c r="B18" s="18">
+    <row r="18">
+      <c r="A18" s="4"/>
+      <c r="B18" s="22">
         <v>161.01</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="22">
         <v>240.55</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="22">
         <v>117.42</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="22">
         <v>175.19</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="22">
         <v>100.08</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="22">
         <v>149.19</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="3"/>
-      <c r="B19" s="18">
+    <row r="19">
+      <c r="A19" s="4"/>
+      <c r="B19" s="22">
         <v>185.16</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="22">
         <v>276.63</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="22">
         <v>135.03</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="22">
         <v>201.48</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="22">
         <v>115.09</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="22">
         <v>171.57</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="3"/>
-      <c r="B20" s="18">
+    <row r="20">
+      <c r="A20" s="4"/>
+      <c r="B20" s="22">
         <v>220.34</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="22">
         <v>329.2</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="22">
         <v>160.68</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="22">
         <v>239.76</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="22">
         <v>136.96</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="22">
         <v>204.17</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="3"/>
-      <c r="B21" s="18">
+    <row r="21">
+      <c r="A21" s="4"/>
+      <c r="B21" s="22">
         <v>275.43</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="22">
         <v>411.49</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="22">
         <v>200.86</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="22">
         <v>299.7</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="22">
         <v>171.2</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="22">
         <v>255.21</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="3"/>
-      <c r="B22" s="18">
+    <row r="22">
+      <c r="A22" s="4"/>
+      <c r="B22" s="22">
         <v>344.28</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="22">
         <v>514.37</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="22">
         <v>251.07</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="22">
         <v>374.63</v>
       </c>
-      <c r="F22" s="18">
-        <v>214</v>
-      </c>
-      <c r="G22" s="18">
+      <c r="F22" s="22">
+        <v>214.0</v>
+      </c>
+      <c r="G22" s="22">
         <v>319.01</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="3"/>
-      <c r="B23" s="18">
+    <row r="23">
+      <c r="A23" s="4"/>
+      <c r="B23" s="22">
         <v>585.28</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="22">
         <v>874.43</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="22">
         <v>426.83</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="22">
         <v>636.87</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="22">
         <v>363.79</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="22">
         <v>542.33</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="3"/>
-      <c r="B24" s="18">
+    <row r="24">
+      <c r="A24" s="4"/>
+      <c r="B24" s="22">
         <v>655.52</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="22">
         <v>979.36</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="22">
         <v>478.05</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="22">
         <v>713.29</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="22">
         <v>407.45</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="22">
         <v>607.4</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" pageOrder="downThenOver" orientation="portrait"/>
-  <headerFooter>
-    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
-    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
-  </headerFooter>
-  <extLst/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>